--- a/Excel_export/2025T145_heating030.xlsx
+++ b/Excel_export/2025T145_heating030.xlsx
@@ -1070,16 +1070,16 @@
     <t>UTC timestamp in ISO 8601 format</t>
   </si>
   <si>
-    <t>Raw GPS latitude from NetCDF temperature axis; interpolated to heating axes when needed</t>
+    <t>Raw GPS latitude on this data time axis</t>
   </si>
   <si>
-    <t>Raw GPS longitude from NetCDF temperature axis; interpolated to heating axes when needed</t>
+    <t>Raw GPS longitude on this data time axis</t>
   </si>
   <si>
-    <t>Quality-controlled latitude; interpolated to heating axes when needed</t>
+    <t>Quality-controlled latitude on this data time axis</t>
   </si>
   <si>
-    <t>Quality-controlled longitude; interpolated to heating axes when needed</t>
+    <t>Quality-controlled longitude on this data time axis</t>
   </si>
   <si>
     <t>1=original; 2=interpolated; 3=invalid; 4=edge extrapolated; 5=long-gap filled</t>
@@ -2254,10 +2254,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>84.416799999999995</v>
+        <v>84.416899999999998</v>
       </c>
       <c r="C2" s="0">
-        <v>-17.967400000000001</v>
+        <v>-17.969100000000001</v>
       </c>
       <c r="D2" s="0">
         <v>84.393799999999999</v>
@@ -3011,10 +3011,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>84.349199999999996</v>
+        <v>84.359800000000007</v>
       </c>
       <c r="C3" s="0">
-        <v>-17.7438</v>
+        <v>-17.397500000000001</v>
       </c>
       <c r="D3" s="0">
         <v>84.382900000000006</v>
@@ -3768,10 +3768,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>84.270300000000006</v>
+        <v>84.247100000000003</v>
       </c>
       <c r="C4" s="0">
-        <v>-17.866499999999998</v>
+        <v>-17.417999999999999</v>
       </c>
       <c r="D4" s="0">
         <v>84.281099999999995</v>
@@ -4525,10 +4525,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>84.141300000000001</v>
+        <v>84.153899999999993</v>
       </c>
       <c r="C5" s="0">
-        <v>-17.1053</v>
+        <v>-17.878699999999998</v>
       </c>
       <c r="D5" s="0">
         <v>84.141300000000001</v>
@@ -5282,10 +5282,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>84.029200000000003</v>
+        <v>84.062700000000007</v>
       </c>
       <c r="C6" s="0">
-        <v>-17.1295</v>
+        <v>-17.23</v>
       </c>
       <c r="D6" s="0">
         <v>84.041200000000003</v>
@@ -6039,10 +6039,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>83.973399999999998</v>
+        <v>83.936700000000002</v>
       </c>
       <c r="C7" s="0">
-        <v>-17.6785</v>
+        <v>-16.5044</v>
       </c>
       <c r="D7" s="0">
         <v>83.984099999999998</v>
@@ -6796,10 +6796,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>83.409999999999997</v>
+        <v>83.844099999999997</v>
       </c>
       <c r="C8" s="0">
-        <v>-7.5476999999999999</v>
+        <v>-16.955300000000001</v>
       </c>
       <c r="D8" s="0">
         <v>83.852900000000005</v>
@@ -7553,10 +7553,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>83.727900000000005</v>
+        <v>83.412199999999999</v>
       </c>
       <c r="C9" s="0">
-        <v>-15.944900000000001</v>
+        <v>-9.4109999999999996</v>
       </c>
       <c r="D9" s="0">
         <v>83.751800000000003</v>
@@ -8310,10 +8310,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>83.659199999999998</v>
+        <v>83.566999999999993</v>
       </c>
       <c r="C10" s="0">
-        <v>-15.766</v>
+        <v>-13.8812</v>
       </c>
       <c r="D10" s="0">
         <v>83.668700000000001</v>
@@ -9067,10 +9067,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>83.609399999999994</v>
+        <v>83.643699999999995</v>
       </c>
       <c r="C11" s="0">
-        <v>-14.971500000000001</v>
+        <v>-15.0565</v>
       </c>
       <c r="D11" s="0">
         <v>83.618399999999994</v>
@@ -9824,10 +9824,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>83.318799999999996</v>
+        <v>83.448899999999995</v>
       </c>
       <c r="C12" s="0">
-        <v>-10.536899999999999</v>
+        <v>-12.665100000000001</v>
       </c>
       <c r="D12" s="0">
         <v>83.618300000000005</v>
@@ -10581,10 +10581,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>83.395099999999999</v>
+        <v>83.414100000000005</v>
       </c>
       <c r="C13" s="0">
-        <v>-11.9275</v>
+        <v>-12.5966</v>
       </c>
       <c r="D13" s="0">
         <v>83.562700000000007</v>
@@ -11338,10 +11338,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>83.545299999999997</v>
+        <v>83.467500000000001</v>
       </c>
       <c r="C14" s="0">
-        <v>-14.4961</v>
+        <v>-13.348699999999999</v>
       </c>
       <c r="D14" s="0">
         <v>83.528300000000002</v>
@@ -12095,10 +12095,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>83.545400000000001</v>
+        <v>83.761899999999997</v>
       </c>
       <c r="C15" s="0">
-        <v>-13.183</v>
+        <v>-16.036000000000001</v>
       </c>
       <c r="D15" s="0">
         <v>83.545199999999994</v>
@@ -12852,10 +12852,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>83.790899999999993</v>
+        <v>83.817499999999995</v>
       </c>
       <c r="C16" s="0">
-        <v>-13.706799999999999</v>
+        <v>-14.116899999999999</v>
       </c>
       <c r="D16" s="0">
         <v>83.639499999999998</v>
@@ -13609,10 +13609,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>83.989400000000003</v>
+        <v>83.950400000000002</v>
       </c>
       <c r="C17" s="0">
-        <v>-15.928000000000001</v>
+        <v>-14.7782</v>
       </c>
       <c r="D17" s="0">
         <v>83.636200000000002</v>
@@ -14366,10 +14366,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>84.036500000000004</v>
+        <v>83.782799999999995</v>
       </c>
       <c r="C18" s="0">
-        <v>-14.274800000000001</v>
+        <v>-10.9855</v>
       </c>
       <c r="D18" s="0">
         <v>83.782899999999998</v>
@@ -15123,10 +15123,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>84.180499999999995</v>
+        <v>84.171899999999994</v>
       </c>
       <c r="C19" s="0">
-        <v>-15.7386</v>
+        <v>-16.090800000000002</v>
       </c>
       <c r="D19" s="0">
         <v>83.8245</v>
@@ -15880,10 +15880,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>84.291399999999996</v>
+        <v>84.219999999999999</v>
       </c>
       <c r="C20" s="0">
-        <v>-18.296800000000001</v>
+        <v>-16.971900000000002</v>
       </c>
       <c r="D20" s="0">
         <v>83.869900000000001</v>
@@ -16637,10 +16637,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>84.163600000000002</v>
+        <v>83.899100000000004</v>
       </c>
       <c r="C21" s="0">
-        <v>-17.527799999999999</v>
+        <v>-13.954499999999999</v>
       </c>
       <c r="D21" s="0">
         <v>83.842699999999994</v>
@@ -17394,10 +17394,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>84.268500000000003</v>
+        <v>84.303899999999999</v>
       </c>
       <c r="C22" s="0">
-        <v>-18.983599999999999</v>
+        <v>-19.119700000000002</v>
       </c>
       <c r="D22" s="0">
         <v>83.765199999999993</v>
@@ -18151,10 +18151,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>83.915099999999995</v>
+        <v>83.791499999999999</v>
       </c>
       <c r="C23" s="0">
-        <v>-14.6884</v>
+        <v>-13.7148</v>
       </c>
       <c r="D23" s="0">
         <v>83.791399999999996</v>
@@ -18908,10 +18908,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>84.332999999999998</v>
+        <v>83.748400000000004</v>
       </c>
       <c r="C24" s="0">
-        <v>-20.363</v>
+        <v>-13.9564</v>
       </c>
       <c r="D24" s="0">
         <v>83.787199999999999</v>
@@ -19665,10 +19665,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>84.461200000000005</v>
+        <v>84.462400000000002</v>
       </c>
       <c r="C25" s="0">
-        <v>-22.029199999999999</v>
+        <v>-22.077200000000001</v>
       </c>
       <c r="D25" s="0">
         <v>83.713800000000006</v>
@@ -20422,10 +20422,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>83.510800000000003</v>
+        <v>83.459199999999996</v>
       </c>
       <c r="C26" s="0">
-        <v>-14.416700000000001</v>
+        <v>-13.6548</v>
       </c>
       <c r="D26" s="0">
         <v>83.510800000000003</v>
@@ -21179,10 +21179,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>83.287800000000004</v>
+        <v>83.286199999999994</v>
       </c>
       <c r="C27" s="0">
-        <v>-13.2698</v>
+        <v>-13.293200000000001</v>
       </c>
       <c r="D27" s="0">
         <v>83.286000000000001</v>
@@ -21936,10 +21936,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>83.082999999999998</v>
+        <v>83.073999999999998</v>
       </c>
       <c r="C28" s="0">
-        <v>-12.577999999999999</v>
+        <v>-12.8833</v>
       </c>
       <c r="D28" s="0">
         <v>83.081800000000001</v>
@@ -22693,10 +22693,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>82.880200000000002</v>
+        <v>82.888400000000004</v>
       </c>
       <c r="C29" s="0">
-        <v>-13.123200000000001</v>
+        <v>-12.8428</v>
       </c>
       <c r="D29" s="0">
         <v>82.880200000000002</v>
@@ -23450,10 +23450,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>82.742999999999995</v>
+        <v>82.802999999999997</v>
       </c>
       <c r="C30" s="0">
-        <v>-12.8504</v>
+        <v>-13.273300000000001</v>
       </c>
       <c r="D30" s="0">
         <v>82.741600000000005</v>
@@ -24207,10 +24207,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>82.5291</v>
+        <v>82.529200000000003</v>
       </c>
       <c r="C31" s="0">
-        <v>-12.498699999999999</v>
+        <v>-12.498900000000001</v>
       </c>
       <c r="D31" s="0">
         <v>82.5291</v>
@@ -24964,10 +24964,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>82.447800000000001</v>
+        <v>82.419399999999996</v>
       </c>
       <c r="C32" s="0">
-        <v>-11.513999999999999</v>
+        <v>-11.2034</v>
       </c>
       <c r="D32" s="0">
         <v>82.447100000000006</v>
@@ -25721,10 +25721,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>82.416700000000006</v>
+        <v>82.445599999999999</v>
       </c>
       <c r="C33" s="0">
-        <v>-9.8181999999999992</v>
+        <v>-10.1343</v>
       </c>
       <c r="D33" s="0">
         <v>82.416700000000006</v>
@@ -26478,10 +26478,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>82.334199999999996</v>
+        <v>82.294499999999999</v>
       </c>
       <c r="C34" s="0">
-        <v>-8.3668999999999993</v>
+        <v>-8.5836000000000006</v>
       </c>
       <c r="D34" s="0">
         <v>82.334800000000001</v>
@@ -27235,10 +27235,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>82.298900000000003</v>
+        <v>82.239400000000003</v>
       </c>
       <c r="C35" s="0">
-        <v>-8.3285</v>
+        <v>-7.7173999999999996</v>
       </c>
       <c r="D35" s="0">
         <v>82.299800000000005</v>
@@ -27992,10 +27992,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>82.207999999999998</v>
+        <v>82.279300000000006</v>
       </c>
       <c r="C36" s="0">
-        <v>-7.4381000000000004</v>
+        <v>-7.4889000000000001</v>
       </c>
       <c r="D36" s="0">
         <v>82.244</v>
@@ -28749,10 +28749,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>82.4071</v>
+        <v>82.367000000000004</v>
       </c>
       <c r="C37" s="0">
-        <v>-6.5187999999999997</v>
+        <v>-6.4892000000000003</v>
       </c>
       <c r="D37" s="0">
         <v>82.4071</v>
@@ -29506,10 +29506,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>82.492400000000004</v>
+        <v>82.495900000000006</v>
       </c>
       <c r="C38" s="0">
-        <v>-5.4966999999999997</v>
+        <v>-5.2192999999999996</v>
       </c>
       <c r="D38" s="0">
         <v>82.4572</v>
@@ -30263,10 +30263,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>82.353700000000003</v>
+        <v>82.395799999999994</v>
       </c>
       <c r="C39" s="0">
-        <v>-4.6265999999999998</v>
+        <v>-4.6063000000000001</v>
       </c>
       <c r="D39" s="0">
         <v>82.355500000000006</v>
@@ -31020,10 +31020,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>82.290199999999999</v>
+        <v>82.252200000000002</v>
       </c>
       <c r="C40" s="0">
-        <v>-4.0095000000000001</v>
+        <v>-4.2560000000000002</v>
       </c>
       <c r="D40" s="0">
         <v>82.287599999999998</v>
@@ -31777,10 +31777,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>82.257099999999994</v>
+        <v>82.221699999999998</v>
       </c>
       <c r="C41" s="0">
-        <v>-3.7321</v>
+        <v>-3.7084000000000001</v>
       </c>
       <c r="D41" s="0">
         <v>82.257099999999994</v>
@@ -32534,10 +32534,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>82.334400000000002</v>
+        <v>82.374499999999998</v>
       </c>
       <c r="C42" s="0">
-        <v>-2.9544999999999999</v>
+        <v>-2.9702000000000002</v>
       </c>
       <c r="D42" s="0">
         <v>82.334400000000002</v>
@@ -33291,10 +33291,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>82.488100000000003</v>
+        <v>82.451499999999996</v>
       </c>
       <c r="C43" s="0">
-        <v>-1.6434</v>
+        <v>-1.9092</v>
       </c>
       <c r="D43" s="0">
         <v>82.488100000000003</v>
@@ -34048,10 +34048,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>82.525300000000001</v>
+        <v>82.525899999999993</v>
       </c>
       <c r="C44" s="0">
-        <v>-1.0993999999999999</v>
+        <v>-0.82630000000000003</v>
       </c>
       <c r="D44" s="0">
         <v>82.525300000000001</v>
@@ -34805,10 +34805,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>82.562200000000004</v>
+        <v>82.5976</v>
       </c>
       <c r="C45" s="0">
-        <v>0.0011000000000000001</v>
+        <v>-0.27810000000000001</v>
       </c>
       <c r="D45" s="0">
         <v>82.562100000000001</v>
@@ -35562,10 +35562,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>82.596800000000002</v>
+        <v>82.597399999999993</v>
       </c>
       <c r="C46" s="0">
-        <v>0.83530000000000004</v>
+        <v>0.55630000000000002</v>
       </c>
       <c r="D46" s="0">
         <v>82.562200000000004</v>
@@ -36319,10 +36319,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>82.596800000000002</v>
+        <v>82.596400000000003</v>
       </c>
       <c r="C47" s="0">
-        <v>0.83540000000000003</v>
+        <v>1.1124000000000001</v>
       </c>
       <c r="D47" s="0">
         <v>82.596199999999996</v>
@@ -37076,10 +37076,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>82.5608</v>
+        <v>82.561400000000006</v>
       </c>
       <c r="C48" s="0">
-        <v>1.107</v>
+        <v>0.83030000000000004</v>
       </c>
       <c r="D48" s="0">
         <v>82.5608</v>
@@ -37833,10 +37833,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>82.596400000000003</v>
+        <v>82.561400000000006</v>
       </c>
       <c r="C49" s="0">
-        <v>1.1124000000000001</v>
+        <v>0.83030000000000004</v>
       </c>
       <c r="D49" s="0">
         <v>82.596400000000003</v>
@@ -38590,10 +38590,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>82.631900000000002</v>
+        <v>82.671199999999999</v>
       </c>
       <c r="C50" s="0">
-        <v>1.1177999999999999</v>
+        <v>1.4039999999999999</v>
       </c>
       <c r="D50" s="0">
         <v>82.630200000000002</v>
@@ -39347,10 +39347,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>82.593500000000006</v>
+        <v>82.629000000000005</v>
       </c>
       <c r="C51" s="0">
-        <v>1.9472</v>
+        <v>1.9557</v>
       </c>
       <c r="D51" s="0">
         <v>82.593500000000006</v>
@@ -40104,10 +40104,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>82.5565</v>
+        <v>82.521199999999993</v>
       </c>
       <c r="C52" s="0">
-        <v>2.2166000000000001</v>
+        <v>2.2025999999999999</v>
       </c>
       <c r="D52" s="0">
         <v>82.5565</v>
@@ -40861,10 +40861,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>82.447199999999995</v>
+        <v>82.480900000000005</v>
       </c>
       <c r="C53" s="0">
-        <v>2.7263000000000002</v>
+        <v>3.0127999999999999</v>
       </c>
       <c r="D53" s="0">
         <v>82.447199999999995</v>
@@ -42375,10 +42375,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>82.365399999999994</v>
+        <v>82.332300000000004</v>
       </c>
       <c r="C55" s="0">
-        <v>3.5078</v>
+        <v>3.2244999999999999</v>
       </c>
       <c r="D55" s="0">
         <v>82.334299999999999</v>
@@ -43132,10 +43132,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>82.263199999999998</v>
+        <v>82.261399999999995</v>
       </c>
       <c r="C56" s="0">
-        <v>2.9287999999999998</v>
+        <v>3.1945999999999999</v>
       </c>
       <c r="D56" s="0">
         <v>82.261300000000006</v>
@@ -43889,10 +43889,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>82.229299999999995</v>
+        <v>82.265100000000004</v>
       </c>
       <c r="C57" s="0">
-        <v>2.6505999999999998</v>
+        <v>2.6629999999999998</v>
       </c>
       <c r="D57" s="0">
         <v>82.225800000000007</v>
@@ -44646,10 +44646,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>82.082700000000003</v>
+        <v>82.048900000000003</v>
       </c>
       <c r="C58" s="0">
-        <v>2.6015000000000001</v>
+        <v>2.3319999999999999</v>
       </c>
       <c r="D58" s="0">
         <v>82.082700000000003</v>
@@ -45403,10 +45403,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>81.942700000000002</v>
+        <v>81.942499999999995</v>
       </c>
       <c r="C59" s="0">
-        <v>2.3008999999999999</v>
+        <v>2.3008000000000002</v>
       </c>
       <c r="D59" s="0">
         <v>81.942499999999995</v>
@@ -46160,10 +46160,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>81.792599999999993</v>
+        <v>81.794200000000004</v>
       </c>
       <c r="C60" s="0">
-        <v>2.7621000000000002</v>
+        <v>2.5114000000000001</v>
       </c>
       <c r="D60" s="0">
         <v>81.792599999999993</v>
@@ -46917,10 +46917,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>81.687600000000003</v>
+        <v>81.652500000000003</v>
       </c>
       <c r="C61" s="0">
-        <v>2.4786999999999999</v>
+        <v>2.4681000000000002</v>
       </c>
       <c r="D61" s="0">
         <v>81.684299999999993</v>
@@ -47674,10 +47674,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>81.471299999999999</v>
+        <v>81.507099999999994</v>
       </c>
       <c r="C62" s="0">
-        <v>2.1755</v>
+        <v>2.1840000000000002</v>
       </c>
       <c r="D62" s="0">
         <v>81.471299999999999</v>
@@ -48431,10 +48431,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>81.035700000000006</v>
+        <v>81.036000000000001</v>
       </c>
       <c r="C63" s="0">
-        <v>2.0691999999999999</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="D63" s="0">
         <v>81.035700000000006</v>
@@ -49188,10 +49188,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>80.823499999999996</v>
+        <v>80.788399999999996</v>
       </c>
       <c r="C64" s="0">
-        <v>0.2235</v>
+        <v>0.2238</v>
       </c>
       <c r="D64" s="0">
         <v>80.823499999999996</v>
@@ -49945,10 +49945,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>80.682199999999995</v>
+        <v>80.717699999999994</v>
       </c>
       <c r="C65" s="0">
-        <v>-0.222</v>
+        <v>0</v>
       </c>
       <c r="D65" s="0">
         <v>80.682199999999995</v>
@@ -50702,10 +50702,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>80.4983</v>
+        <v>80.498699999999999</v>
       </c>
       <c r="C66" s="0">
-        <v>-0.86799999999999999</v>
+        <v>-0.86809999999999998</v>
       </c>
       <c r="D66" s="0">
         <v>80.4983</v>
@@ -52216,7 +52216,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>80.458799999999997</v>
+        <v>80.499799999999993</v>
       </c>
       <c r="C68" s="0">
         <v>0</v>
@@ -52973,10 +52973,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>80.569800000000001</v>
+        <v>80.5702</v>
       </c>
       <c r="C69" s="0">
-        <v>0.65600000000000003</v>
+        <v>0.43740000000000001</v>
       </c>
       <c r="D69" s="0">
         <v>80.569800000000001</v>
@@ -53730,10 +53730,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>80.568100000000001</v>
+        <v>80.534000000000006</v>
       </c>
       <c r="C70" s="0">
-        <v>1.0919000000000001</v>
+        <v>0.87139999999999995</v>
       </c>
       <c r="D70" s="0">
         <v>80.568299999999994</v>
@@ -54487,10 +54487,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>80.281400000000005</v>
+        <v>80.316599999999994</v>
       </c>
       <c r="C71" s="0">
-        <v>0.42359999999999998</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="D71" s="0">
         <v>80.281099999999995</v>
@@ -55244,10 +55244,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="0">
-        <v>80.063699999999997</v>
+        <v>80.099000000000004</v>
       </c>
       <c r="C72" s="0">
-        <v>-0.20979999999999999</v>
+        <v>-0.41670000000000001</v>
       </c>
       <c r="D72" s="0">
         <v>80.063699999999997</v>
@@ -56001,10 +56001,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="0">
-        <v>79.873500000000007</v>
+        <v>79.873699999999999</v>
       </c>
       <c r="C73" s="0">
-        <v>-2.2431999999999999</v>
+        <v>-2.2418</v>
       </c>
       <c r="D73" s="0">
         <v>79.873699999999999</v>
@@ -56758,10 +56758,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="0">
-        <v>79.964399999999998</v>
+        <v>79.9666</v>
       </c>
       <c r="C74" s="0">
-        <v>-3.9098999999999999</v>
+        <v>-3.7046000000000001</v>
       </c>
       <c r="D74" s="0">
         <v>79.931399999999996</v>
@@ -57515,10 +57515,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="0">
-        <v>79.9238</v>
+        <v>79.921300000000002</v>
       </c>
       <c r="C75" s="0">
-        <v>-4.3052999999999999</v>
+        <v>-4.5086000000000004</v>
       </c>
       <c r="D75" s="0">
         <v>79.924000000000007</v>
@@ -58272,10 +58272,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="0">
-        <v>79.885900000000007</v>
+        <v>79.850899999999996</v>
       </c>
       <c r="C76" s="0">
-        <v>-4.4924999999999997</v>
+        <v>-4.4767000000000001</v>
       </c>
       <c r="D76" s="0">
         <v>79.883099999999999</v>
@@ -59029,10 +59029,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="0">
-        <v>79.733400000000003</v>
+        <v>79.7363</v>
       </c>
       <c r="C77" s="0">
-        <v>-4.8296000000000001</v>
+        <v>-4.6300999999999997</v>
       </c>
       <c r="D77" s="0">
         <v>79.7363</v>
@@ -59789,7 +59789,7 @@
         <v>79.589299999999994</v>
       </c>
       <c r="C78" s="0">
-        <v>-4.5651999999999999</v>
+        <v>-4.5659999999999998</v>
       </c>
       <c r="D78" s="0">
         <v>79.592100000000002</v>
@@ -60543,10 +60543,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="0">
-        <v>79.629800000000003</v>
+        <v>79.592100000000002</v>
       </c>
       <c r="C79" s="0">
-        <v>-4.1856</v>
+        <v>-4.3682999999999996</v>
       </c>
       <c r="D79" s="0">
         <v>79.627200000000002</v>
@@ -61300,10 +61300,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="0">
-        <v>79.621700000000004</v>
+        <v>79.663200000000003</v>
       </c>
       <c r="C80" s="0">
-        <v>-4.7801999999999998</v>
+        <v>-4.7968000000000002</v>
       </c>
       <c r="D80" s="0">
         <v>79.624499999999998</v>
@@ -62057,10 +62057,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="0">
-        <v>79.724100000000007</v>
+        <v>79.720600000000005</v>
       </c>
       <c r="C81" s="0">
-        <v>-5.4302000000000001</v>
+        <v>-5.6307</v>
       </c>
       <c r="D81" s="0">
         <v>79.724100000000007</v>
@@ -62814,10 +62814,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="0">
-        <v>79.8005</v>
+        <v>79.730400000000003</v>
       </c>
       <c r="C82" s="0">
-        <v>-5.0660999999999996</v>
+        <v>-5.0307000000000004</v>
       </c>
       <c r="D82" s="0">
         <v>79.765500000000003</v>
@@ -63571,10 +63571,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="0">
-        <v>79.727400000000003</v>
+        <v>79.797499999999999</v>
       </c>
       <c r="C83" s="0">
-        <v>-5.2302</v>
+        <v>-5.2676999999999996</v>
       </c>
       <c r="D83" s="0">
         <v>79.762200000000007</v>
@@ -64328,10 +64328,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="0">
-        <v>79.698300000000003</v>
+        <v>79.730400000000003</v>
       </c>
       <c r="C84" s="0">
-        <v>-4.8135000000000003</v>
+        <v>-5.0307000000000004</v>
       </c>
       <c r="D84" s="0">
         <v>79.698300000000003</v>
@@ -65085,10 +65085,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="0">
-        <v>79.739000000000004</v>
+        <v>79.739099999999993</v>
       </c>
       <c r="C85" s="0">
-        <v>-4.4295</v>
+        <v>-4.4295999999999998</v>
       </c>
       <c r="D85" s="0">
         <v>79.733400000000003</v>
@@ -65842,10 +65842,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="0">
-        <v>79.665700000000001</v>
+        <v>79.703999999999994</v>
       </c>
       <c r="C86" s="0">
-        <v>-4.5975999999999999</v>
+        <v>-4.4141000000000004</v>
       </c>
       <c r="D86" s="0">
         <v>79.665700000000001</v>
@@ -66599,10 +66599,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="0">
-        <v>79.450699999999998</v>
+        <v>79.334100000000007</v>
       </c>
       <c r="C87" s="0">
-        <v>-4.3102999999999998</v>
+        <v>-4.6510999999999996</v>
       </c>
       <c r="D87" s="0">
         <v>79.368799999999993</v>
@@ -67356,10 +67356,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="0">
-        <v>79.116399999999999</v>
+        <v>79.084500000000006</v>
       </c>
       <c r="C88" s="0">
-        <v>-4.5571999999999999</v>
+        <v>-4.3552</v>
       </c>
       <c r="D88" s="0">
         <v>79.113600000000005</v>
@@ -68113,10 +68113,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="0">
-        <v>78.942099999999996</v>
+        <v>78.942400000000006</v>
       </c>
       <c r="C89" s="0">
-        <v>-3.9258000000000002</v>
+        <v>-3.9258999999999999</v>
       </c>
       <c r="D89" s="0">
         <v>78.942099999999996</v>
@@ -68870,10 +68870,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="0">
-        <v>78.614199999999997</v>
+        <v>78.612799999999993</v>
       </c>
       <c r="C90" s="0">
-        <v>-3.6326999999999998</v>
+        <v>-3.8140999999999998</v>
       </c>
       <c r="D90" s="0">
         <v>78.614199999999997</v>
@@ -69627,10 +69627,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="0">
-        <v>77.905600000000007</v>
+        <v>77.946100000000001</v>
       </c>
       <c r="C91" s="0">
-        <v>-3.9434999999999998</v>
+        <v>-4.1223000000000001</v>
       </c>
       <c r="D91" s="0">
         <v>77.905600000000007</v>
@@ -70384,10 +70384,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="0">
-        <v>76.997500000000002</v>
+        <v>77.401499999999999</v>
       </c>
       <c r="C92" s="0">
-        <v>-4.3669000000000002</v>
+        <v>-3.7812999999999999</v>
       </c>
       <c r="D92" s="0">
         <v>76.997500000000002</v>
@@ -71147,7 +71147,7 @@
   <cols>
     <col min="1" max="1" width="73.5703125" customWidth="true"/>
     <col min="2" max="2" width="6" customWidth="true"/>
-    <col min="3" max="3" width="83.85546875" customWidth="true"/>
+    <col min="3" max="3" width="75.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
